--- a/r5-aist-trustworthyai-main/ValueSet-eu-ai-performance-metric-vs.xlsx
+++ b/r5-aist-trustworthyai-main/ValueSet-eu-ai-performance-metric-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:47+00:00</t>
+    <t>2026-06-18T12:04:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Codes for technical quality and performance metrics.</t>
+    <t>Codes for technical quality and performance metrics (QUAL-01).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t>specificity</t>
+  </si>
+  <si>
+    <t>robustness</t>
   </si>
   <si>
     <t>System URI</t>
@@ -364,7 +367,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -399,18 +402,24 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
         <v>31</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/r5-aist-trustworthyai-main/ValueSet-eu-ai-performance-metric-vs.xlsx
+++ b/r5-aist-trustworthyai-main/ValueSet-eu-ai-performance-metric-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <t>Property</t>
   </si>
@@ -36,13 +36,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>EU_AI_PerformanceMetricVS</t>
+    <t>EUAIPerformanceMetricVS</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>AI Performance Metric ValueSet</t>
+    <t>EU AI Performance Metric Value Set</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:04:51+00:00</t>
+    <t>2026-07-31T11:07:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Codes for technical quality and performance metrics (QUAL-01).</t>
+    <t>Performance characteristics that may be documented for an AI system.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -93,25 +93,16 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Concept</t>
-  </si>
-  <si>
-    <t>accuracy</t>
-  </si>
-  <si>
-    <t>sensitivity</t>
-  </si>
-  <si>
-    <t>specificity</t>
-  </si>
-  <si>
-    <t>robustness</t>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>All codes</t>
   </si>
   <si>
     <t>System URI</t>
   </si>
   <si>
-    <t>http://example.org/fhir/eu-ai-transparency/CodeSystem/EUAIActCodeSystem</t>
+    <t>http://example.org/fhir/eu-ai-transparency/CodeSystem/eu-ai-performance-metric-cs</t>
   </si>
 </sst>
 </file>
@@ -367,7 +358,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -378,48 +369,26 @@
       <c r="A1" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>20</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>27</v>
       </c>
-      <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>19</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>29</v>
-      </c>
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B5" s="2"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/r5-aist-trustworthyai-main/ValueSet-eu-ai-performance-metric-vs.xlsx
+++ b/r5-aist-trustworthyai-main/ValueSet-eu-ai-performance-metric-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T11:07:29+00:00</t>
+    <t>2026-09-02T10:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/ValueSet-eu-ai-performance-metric-vs.xlsx
+++ b/r5-aist-trustworthyai-main/ValueSet-eu-ai-performance-metric-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:48:14+00:00</t>
+    <t>2026-09-03T11:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/ValueSet-eu-ai-performance-metric-vs.xlsx
+++ b/r5-aist-trustworthyai-main/ValueSet-eu-ai-performance-metric-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:53:05+00:00</t>
+    <t>2026-09-07T08:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
